--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA744E9-77C7-4A86-8CB0-BB4F261D217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E801770-1218-4764-A8BD-C8EC28C1E60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -39,6 +39,18 @@
   </si>
   <si>
     <t>{0} のダメージ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}%</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}/{1}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}F</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -412,7 +424,9 @@
       <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -421,7 +435,9 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -430,7 +446,9 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,27 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E801770-1218-4764-A8BD-C8EC28C1E60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7778716D-BE6E-4B4F-BA46-07742A77287C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="855" yWindow="-15090" windowWidth="14295" windowHeight="13725" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
     <sheet name="Character" sheetId="2" r:id="rId2"/>
     <sheet name="Item" sheetId="4" r:id="rId3"/>
     <sheet name="Log" sheetId="5" r:id="rId4"/>
+    <sheet name="Action" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="13">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -38,10 +48,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>{0} のダメージ！</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{0}%</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -51,6 +57,47 @@
   </si>
   <si>
     <t>{0}F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} の {1}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} に {1} のダメージ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵A</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵B</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイやー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -425,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -436,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -447,7 +494,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -480,8 +527,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B199E2-5003-4F2A-8FEF-40F232A9A533}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -504,7 +554,9 @@
       <c r="A2" s="2">
         <v>10000</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -513,7 +565,9 @@
       <c r="A3" s="2">
         <v>10001</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -522,7 +576,9 @@
       <c r="A4" s="2">
         <v>10002</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -531,19 +587,41 @@
       <c r="A5" s="2">
         <v>10003</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>11999</v>
-      </c>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>10004</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>10005</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>11999</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -631,6 +709,87 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>14000</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>14010</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>14011</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>14012</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>15999</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2A82C7-4333-4A51-BE45-F7D6B9863B69}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -653,10 +812,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -664,7 +823,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>14001</v>
+        <v>16001</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -673,7 +832,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>14002</v>
+        <v>16002</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -682,7 +841,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>14003</v>
+        <v>16003</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -690,8 +849,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>15999</v>
+      <c r="A6" s="2">
+        <v>17999</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7778716D-BE6E-4B4F-BA46-07742A77287C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C437C72B-31A6-458A-8816-094E3E3EE1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="-15090" windowWidth="14295" windowHeight="13725" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12600" yWindow="-14310" windowWidth="17865" windowHeight="16305" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -98,6 +98,55 @@
   </si>
   <si>
     <t>プレイやー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を拾った</t>
+    <rPh sb="5" eb="6">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムがいっぱいで {0} を拾えなかった</t>
+    <rPh sb="16" eb="17">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬1</t>
+    <rPh sb="0" eb="1">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーションA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法の杖</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツエ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -632,8 +681,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690492FB-2015-41D4-A9BA-80BB0E1570F4}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -656,7 +708,9 @@
       <c r="A2" s="2">
         <v>12000</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -665,37 +719,72 @@
       <c r="A3" s="2">
         <v>12001</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>12002</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>12100</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>12003</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>12101</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>13999</v>
-      </c>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>12200</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>12201</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>12202</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>13999</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -709,7 +798,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -753,18 +842,22 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>14011</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>14020</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>14012</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>14021</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C437C72B-31A6-458A-8816-094E3E3EE1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB63CD62-BCE5-4196-8EC5-09F2B1D68692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12600" yWindow="-14310" windowWidth="17865" windowHeight="16305" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -146,6 +146,30 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} は {1} を使った</t>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} の満腹度が {1} 回復した</t>
+    <rPh sb="5" eb="8">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} のHPが {1} 回復した</t>
+    <rPh sb="13" eb="15">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -795,7 +819,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3255BB-287B-4B5C-8F0A-2D76258E0DFF}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
@@ -831,10 +855,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>14010</v>
+        <v>14001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -842,10 +866,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>14020</v>
+        <v>14002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -853,23 +877,74 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>14021</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>14003</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>15999</v>
+      <c r="A6" s="2">
+        <v>14004</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>14010</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>14011</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>14020</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>14021</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>15999</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB63CD62-BCE5-4196-8EC5-09F2B1D68692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98940526-095F-4DBA-9497-4EB3DABC2CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -170,6 +170,34 @@
     <t>{0} のHPが {1} 回復した</t>
     <rPh sb="13" eb="15">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使う</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>置く</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外す</t>
+    <rPh sb="0" eb="1">
+      <t>ハズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -520,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -583,13 +611,75 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <v>9999</v>
-      </c>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>9999</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98940526-095F-4DBA-9497-4EB3DABC2CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAD6F0-66D6-46F5-98D9-025402BE825B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -198,6 +198,59 @@
     <t>外す</t>
     <rPh sb="0" eb="1">
       <t>ハズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を置いた</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を置けなかった</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼けた食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐った食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒こげの食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -795,10 +848,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690492FB-2015-41D4-A9BA-80BB0E1570F4}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -864,10 +917,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>12200</v>
+        <v>12102</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -875,30 +928,63 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>12201</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12103</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>12202</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>12104</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3">
-        <v>13999</v>
-      </c>
-      <c r="B9" s="2"/>
+      <c r="A9" s="2">
+        <v>12200</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>12201</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>12202</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>13999</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -909,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3255BB-287B-4B5C-8F0A-2D76258E0DFF}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
@@ -1028,13 +1114,35 @@
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3">
-        <v>15999</v>
-      </c>
-      <c r="B11" s="2"/>
+      <c r="A11" s="2">
+        <v>14030</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>14031</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>15999</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAD6F0-66D6-46F5-98D9-025402BE825B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C85FB5F-9EAF-4663-B76B-08CED325C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8835" yWindow="-14355" windowWidth="16995" windowHeight="10170" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -251,6 +251,37 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} は焼けて {1} になってしまった</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} は腐って {1} になってしまった</t>
+    <rPh sb="5" eb="6">
+      <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐らせる</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1055,7 +1086,9 @@
       <c r="A5" s="2">
         <v>14003</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1064,7 +1097,9 @@
       <c r="A6" s="2">
         <v>14004</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1191,7 +1226,9 @@
       <c r="A3" s="2">
         <v>16001</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1200,7 +1237,9 @@
       <c r="A4" s="2">
         <v>16002</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C85FB5F-9EAF-4663-B76B-08CED325C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA51B07-FE08-47C8-A0C4-2DBD06F81347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8835" yWindow="-14355" windowWidth="16995" windowHeight="10170" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -282,6 +282,17 @@
     <t>腐らせる</t>
     <rPh sb="0" eb="1">
       <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}[{1}]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ただの杖</t>
+    <rPh sb="3" eb="4">
+      <t>ツエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -879,7 +890,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690492FB-2015-41D4-A9BA-80BB0E1570F4}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -994,7 +1005,9 @@
       <c r="A10" s="2">
         <v>12201</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1009,13 +1022,24 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="3">
-        <v>13999</v>
-      </c>
-      <c r="B12" s="2"/>
+      <c r="A12" s="2">
+        <v>12299</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>13999</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
